--- a/AC_2009/AC_026.xlsx
+++ b/AC_2009/AC_026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X320"/>
+  <dimension ref="A1:X322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -518,6 +599,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -24514,93 +24596,268 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C320" s="7">
+      <c r="A320" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B320" s="9" t="inlineStr"/>
+      <c r="C320" s="10">
         <f>SUM(C6:C319)</f>
         <v/>
       </c>
-      <c r="D320" s="7">
+      <c r="D320" s="10">
         <f>SUM(D6:D319)</f>
         <v/>
       </c>
-      <c r="E320" s="7">
+      <c r="E320" s="10">
         <f>SUM(E6:E319)</f>
         <v/>
       </c>
-      <c r="F320" s="7">
+      <c r="F320" s="10">
         <f>SUM(F6:F319)</f>
         <v/>
       </c>
-      <c r="G320" s="7">
+      <c r="G320" s="10">
         <f>SUM(G6:G319)</f>
         <v/>
       </c>
-      <c r="H320" s="7">
+      <c r="H320" s="10">
         <f>SUM(H6:H319)</f>
         <v/>
       </c>
-      <c r="I320" s="7">
+      <c r="I320" s="10">
         <f>SUM(I6:I319)</f>
         <v/>
       </c>
-      <c r="J320" s="7">
+      <c r="J320" s="10">
         <f>SUM(J6:J319)</f>
         <v/>
       </c>
-      <c r="K320" s="7">
+      <c r="K320" s="10">
         <f>SUM(K6:K319)</f>
         <v/>
       </c>
-      <c r="L320" s="7">
+      <c r="L320" s="10">
         <f>SUM(L6:L319)</f>
         <v/>
       </c>
-      <c r="M320" s="7">
+      <c r="M320" s="10">
         <f>SUM(M6:M319)</f>
         <v/>
       </c>
-      <c r="N320" s="7">
+      <c r="N320" s="10">
         <f>SUM(N6:N319)</f>
         <v/>
       </c>
-      <c r="O320" s="7">
+      <c r="O320" s="10">
         <f>SUM(O6:O319)</f>
         <v/>
       </c>
-      <c r="P320" s="7">
+      <c r="P320" s="10">
         <f>SUM(P6:P319)</f>
         <v/>
       </c>
-      <c r="Q320" s="7">
+      <c r="Q320" s="10">
         <f>SUM(Q6:Q319)</f>
         <v/>
       </c>
-      <c r="R320" s="7">
+      <c r="R320" s="10">
         <f>SUM(R6:R319)</f>
         <v/>
       </c>
-      <c r="S320" s="7">
+      <c r="S320" s="10">
         <f>SUM(S6:S319)</f>
         <v/>
       </c>
-      <c r="T320" s="7">
+      <c r="T320" s="10">
         <f>SUM(T6:T319)</f>
         <v/>
       </c>
-      <c r="U320" s="7">
+      <c r="U320" s="10">
         <f>SUM(U6:U319)</f>
         <v/>
       </c>
-      <c r="V320" s="7">
+      <c r="V320" s="10">
         <f>SUM(V6:V319)</f>
         <v/>
       </c>
-      <c r="W320" s="7">
+      <c r="W320" s="10">
         <f>SUM(W6:W319)</f>
+        <v/>
+      </c>
+      <c r="X320" s="10">
+        <f>SUM(X6:X319)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="11" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B321" s="12" t="inlineStr"/>
+      <c r="C321" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D321" s="13" t="n">
+        <v>387</v>
+      </c>
+      <c r="E321" s="13" t="n">
+        <v>220</v>
+      </c>
+      <c r="F321" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="G321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J321" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="K321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" s="13" t="n">
+        <v>701</v>
+      </c>
+      <c r="U321" s="13" t="n">
+        <v>242</v>
+      </c>
+      <c r="V321" s="13" t="n">
+        <v>943</v>
+      </c>
+      <c r="W321" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X321" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B322" s="15" t="inlineStr"/>
+      <c r="C322" s="16">
+        <f>C320+C321</f>
+        <v/>
+      </c>
+      <c r="D322" s="16">
+        <f>D320+D321</f>
+        <v/>
+      </c>
+      <c r="E322" s="16">
+        <f>E320+E321</f>
+        <v/>
+      </c>
+      <c r="F322" s="16">
+        <f>F320+F321</f>
+        <v/>
+      </c>
+      <c r="G322" s="16">
+        <f>G320+G321</f>
+        <v/>
+      </c>
+      <c r="H322" s="16">
+        <f>H320+H321</f>
+        <v/>
+      </c>
+      <c r="I322" s="16">
+        <f>I320+I321</f>
+        <v/>
+      </c>
+      <c r="J322" s="16">
+        <f>J320+J321</f>
+        <v/>
+      </c>
+      <c r="K322" s="16">
+        <f>K320+K321</f>
+        <v/>
+      </c>
+      <c r="L322" s="16">
+        <f>L320+L321</f>
+        <v/>
+      </c>
+      <c r="M322" s="16">
+        <f>M320+M321</f>
+        <v/>
+      </c>
+      <c r="N322" s="16">
+        <f>N320+N321</f>
+        <v/>
+      </c>
+      <c r="O322" s="16">
+        <f>O320+O321</f>
+        <v/>
+      </c>
+      <c r="P322" s="16">
+        <f>P320+P321</f>
+        <v/>
+      </c>
+      <c r="Q322" s="16">
+        <f>Q320+Q321</f>
+        <v/>
+      </c>
+      <c r="R322" s="16">
+        <f>R320+R321</f>
+        <v/>
+      </c>
+      <c r="S322" s="16">
+        <f>S320+S321</f>
+        <v/>
+      </c>
+      <c r="T322" s="16">
+        <f>T320+T321</f>
+        <v/>
+      </c>
+      <c r="U322" s="16">
+        <f>U320+U321</f>
+        <v/>
+      </c>
+      <c r="V322" s="16">
+        <f>V320+V321</f>
+        <v/>
+      </c>
+      <c r="W322" s="16">
+        <f>W320+W321</f>
+        <v/>
+      </c>
+      <c r="X322" s="16">
+        <f>X320+X321</f>
         <v/>
       </c>
     </row>

--- a/AC_2009/AC_026.xlsx
+++ b/AC_2009/AC_026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +153,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +195,23 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -599,7 +629,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -24596,267 +24625,267 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="8" t="inlineStr">
+      <c r="A320" s="17" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B320" s="9" t="inlineStr"/>
-      <c r="C320" s="10">
+      <c r="B320" s="18" t="inlineStr"/>
+      <c r="C320" s="19">
         <f>SUM(C6:C319)</f>
         <v/>
       </c>
-      <c r="D320" s="10">
+      <c r="D320" s="19">
         <f>SUM(D6:D319)</f>
         <v/>
       </c>
-      <c r="E320" s="10">
+      <c r="E320" s="19">
         <f>SUM(E6:E319)</f>
         <v/>
       </c>
-      <c r="F320" s="10">
+      <c r="F320" s="19">
         <f>SUM(F6:F319)</f>
         <v/>
       </c>
-      <c r="G320" s="10">
+      <c r="G320" s="19">
         <f>SUM(G6:G319)</f>
         <v/>
       </c>
-      <c r="H320" s="10">
+      <c r="H320" s="19">
         <f>SUM(H6:H319)</f>
         <v/>
       </c>
-      <c r="I320" s="10">
+      <c r="I320" s="19">
         <f>SUM(I6:I319)</f>
         <v/>
       </c>
-      <c r="J320" s="10">
+      <c r="J320" s="19">
         <f>SUM(J6:J319)</f>
         <v/>
       </c>
-      <c r="K320" s="10">
+      <c r="K320" s="19">
         <f>SUM(K6:K319)</f>
         <v/>
       </c>
-      <c r="L320" s="10">
+      <c r="L320" s="19">
         <f>SUM(L6:L319)</f>
         <v/>
       </c>
-      <c r="M320" s="10">
+      <c r="M320" s="19">
         <f>SUM(M6:M319)</f>
         <v/>
       </c>
-      <c r="N320" s="10">
+      <c r="N320" s="19">
         <f>SUM(N6:N319)</f>
         <v/>
       </c>
-      <c r="O320" s="10">
+      <c r="O320" s="19">
         <f>SUM(O6:O319)</f>
         <v/>
       </c>
-      <c r="P320" s="10">
+      <c r="P320" s="19">
         <f>SUM(P6:P319)</f>
         <v/>
       </c>
-      <c r="Q320" s="10">
+      <c r="Q320" s="19">
         <f>SUM(Q6:Q319)</f>
         <v/>
       </c>
-      <c r="R320" s="10">
+      <c r="R320" s="19">
         <f>SUM(R6:R319)</f>
         <v/>
       </c>
-      <c r="S320" s="10">
+      <c r="S320" s="19">
         <f>SUM(S6:S319)</f>
         <v/>
       </c>
-      <c r="T320" s="10">
+      <c r="T320" s="19">
         <f>SUM(T6:T319)</f>
         <v/>
       </c>
-      <c r="U320" s="10">
+      <c r="U320" s="19">
         <f>SUM(U6:U319)</f>
         <v/>
       </c>
-      <c r="V320" s="10">
+      <c r="V320" s="19">
         <f>SUM(V6:V319)</f>
         <v/>
       </c>
-      <c r="W320" s="10">
+      <c r="W320" s="19">
         <f>SUM(W6:W319)</f>
         <v/>
       </c>
-      <c r="X320" s="10">
+      <c r="X320" s="19">
         <f>SUM(X6:X319)</f>
         <v/>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="11" t="inlineStr">
+      <c r="A321" s="20" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B321" s="12" t="inlineStr"/>
-      <c r="C321" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D321" s="13" t="n">
+      <c r="C321" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D321" s="19" t="n">
         <v>387</v>
       </c>
-      <c r="E321" s="13" t="n">
+      <c r="E321" s="19" t="n">
         <v>220</v>
       </c>
-      <c r="F321" s="13" t="n">
+      <c r="F321" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="G321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I321" s="13" t="n">
+      <c r="G321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="J321" s="13" t="n">
+      <c r="J321" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M321" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O321" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="P321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T321" s="13" t="n">
+      <c r="K321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" s="19" t="n">
         <v>701</v>
       </c>
-      <c r="U321" s="13" t="n">
+      <c r="U321" s="19" t="n">
         <v>242</v>
       </c>
-      <c r="V321" s="13" t="n">
+      <c r="V321" s="19" t="n">
         <v>943</v>
       </c>
-      <c r="W321" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X321" s="13" t="n">
+      <c r="W321" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X321" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="14" t="inlineStr">
+      <c r="A322" s="21" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B322" s="15" t="inlineStr"/>
-      <c r="C322" s="16">
+      <c r="B322" s="22" t="inlineStr"/>
+      <c r="C322" s="23">
         <f>C320+C321</f>
         <v/>
       </c>
-      <c r="D322" s="16">
+      <c r="D322" s="23">
         <f>D320+D321</f>
         <v/>
       </c>
-      <c r="E322" s="16">
+      <c r="E322" s="23">
         <f>E320+E321</f>
         <v/>
       </c>
-      <c r="F322" s="16">
+      <c r="F322" s="23">
         <f>F320+F321</f>
         <v/>
       </c>
-      <c r="G322" s="16">
+      <c r="G322" s="23">
         <f>G320+G321</f>
         <v/>
       </c>
-      <c r="H322" s="16">
+      <c r="H322" s="23">
         <f>H320+H321</f>
         <v/>
       </c>
-      <c r="I322" s="16">
+      <c r="I322" s="23">
         <f>I320+I321</f>
         <v/>
       </c>
-      <c r="J322" s="16">
+      <c r="J322" s="23">
         <f>J320+J321</f>
         <v/>
       </c>
-      <c r="K322" s="16">
+      <c r="K322" s="23">
         <f>K320+K321</f>
         <v/>
       </c>
-      <c r="L322" s="16">
+      <c r="L322" s="23">
         <f>L320+L321</f>
         <v/>
       </c>
-      <c r="M322" s="16">
+      <c r="M322" s="23">
         <f>M320+M321</f>
         <v/>
       </c>
-      <c r="N322" s="16">
+      <c r="N322" s="23">
         <f>N320+N321</f>
         <v/>
       </c>
-      <c r="O322" s="16">
+      <c r="O322" s="23">
         <f>O320+O321</f>
         <v/>
       </c>
-      <c r="P322" s="16">
+      <c r="P322" s="23">
         <f>P320+P321</f>
         <v/>
       </c>
-      <c r="Q322" s="16">
+      <c r="Q322" s="23">
         <f>Q320+Q321</f>
         <v/>
       </c>
-      <c r="R322" s="16">
+      <c r="R322" s="23">
         <f>R320+R321</f>
         <v/>
       </c>
-      <c r="S322" s="16">
+      <c r="S322" s="23">
         <f>S320+S321</f>
         <v/>
       </c>
-      <c r="T322" s="16">
+      <c r="T322" s="23">
         <f>T320+T321</f>
         <v/>
       </c>
-      <c r="U322" s="16">
+      <c r="U322" s="23">
         <f>U320+U321</f>
         <v/>
       </c>
-      <c r="V322" s="16">
+      <c r="V322" s="23">
         <f>V320+V321</f>
         <v/>
       </c>
-      <c r="W322" s="16">
+      <c r="W322" s="23">
         <f>W320+W321</f>
         <v/>
       </c>
-      <c r="X322" s="16">
+      <c r="X322" s="23">
         <f>X320+X321</f>
         <v/>
       </c>

--- a/AC_2009/AC_026.xlsx
+++ b/AC_2009/AC_026.xlsx
@@ -297,7 +297,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -333,6 +333,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1459,7 +1462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X322"/>
+  <dimension ref="A1:W322"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="35" customWidth="1" style="1" min="1" max="2"/>
@@ -1482,11 +1485,10 @@
     <col width="17" customWidth="1" style="1" min="21" max="21"/>
     <col width="16" customWidth="1" style="1" min="22" max="22"/>
     <col width="17" customWidth="1" style="1" min="23" max="23"/>
-    <col width="16" customWidth="1" style="1" min="24" max="24"/>
-    <col width="8.851559999999999" customWidth="1" style="1" min="25" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="1" min="24" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.35" customHeight="1" s="24">
+    <row r="1" ht="15.35" customHeight="1" s="25">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ELECTION TO THE APLA, 2009 FROM THE 26-KARIMNAGAR ASSEMBLY CONSTITUENCY</t>
@@ -1514,9 +1516,8 @@
       <c r="U1" s="3" t="n"/>
       <c r="V1" s="3" t="n"/>
       <c r="W1" s="3" t="n"/>
-      <c r="X1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="13.75" customHeight="1" s="24">
+    </row>
+    <row r="2" ht="13.75" customHeight="1" s="25">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ELECTION TO THE APLA, 2009 FROM THE 26-KARIMNAGAR ASSEMBLY CONSTITUENCY</t>
@@ -1544,9 +1545,8 @@
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
       <c r="W2" s="3" t="n"/>
-      <c r="X2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="13.75" customHeight="1" s="24">
+    </row>
+    <row r="3" ht="13.75" customHeight="1" s="25">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Total No. of Electors in Assembly Constituency : 2,61,573 (Including Service Voters)</t>
@@ -1574,9 +1574,8 @@
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
       <c r="W3" s="3" t="n"/>
-      <c r="X3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="4" ht="13.55" customHeight="1" s="25">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -1600,9 +1599,8 @@
       <c r="U4" s="5" t="n"/>
       <c r="V4" s="5" t="n"/>
       <c r="W4" s="5" t="n"/>
-      <c r="X4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="5" ht="13.55" customHeight="1" s="25">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>PS_No</t>
@@ -1713,18 +1711,13 @@
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="W5" s="7" t="inlineStr">
+      <c r="W5" s="8" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
         </is>
       </c>
-      <c r="X5" s="8" t="inlineStr">
-        <is>
-          <t>Checksum_Diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="6" ht="13.55" customHeight="1" s="25">
       <c r="A6" s="9" t="n">
         <v>1</v>
       </c>
@@ -1796,11 +1789,8 @@
       <c r="W6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="7" ht="13.55" customHeight="1" s="25">
       <c r="A7" s="9" t="n">
         <v>2</v>
       </c>
@@ -1872,11 +1862,8 @@
       <c r="W7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X7" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="8" ht="13.55" customHeight="1" s="25">
       <c r="A8" s="9" t="n">
         <v>3</v>
       </c>
@@ -1948,11 +1935,8 @@
       <c r="W8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="9" ht="13.55" customHeight="1" s="25">
       <c r="A9" s="9" t="n">
         <v>4</v>
       </c>
@@ -2024,11 +2008,8 @@
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="10" ht="13.55" customHeight="1" s="25">
       <c r="A10" s="9" t="n">
         <v>5</v>
       </c>
@@ -2100,11 +2081,8 @@
       <c r="W10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="11" ht="13.55" customHeight="1" s="25">
       <c r="A11" s="9" t="n">
         <v>6</v>
       </c>
@@ -2176,11 +2154,8 @@
       <c r="W11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X11" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="12" ht="13.55" customHeight="1" s="25">
       <c r="A12" s="9" t="n">
         <v>7</v>
       </c>
@@ -2252,11 +2227,8 @@
       <c r="W12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X12" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="13" ht="13.55" customHeight="1" s="25">
       <c r="A13" s="9" t="n">
         <v>8</v>
       </c>
@@ -2328,11 +2300,8 @@
       <c r="W13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X13" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="14" ht="13.55" customHeight="1" s="25">
       <c r="A14" s="9" t="n">
         <v>9</v>
       </c>
@@ -2404,11 +2373,8 @@
       <c r="W14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X14" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="15" ht="13.55" customHeight="1" s="25">
       <c r="A15" s="9" t="n">
         <v>10</v>
       </c>
@@ -2480,11 +2446,8 @@
       <c r="W15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="16" ht="13.55" customHeight="1" s="25">
       <c r="A16" s="9" t="n">
         <v>11</v>
       </c>
@@ -2556,11 +2519,8 @@
       <c r="W16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X16" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="17" ht="13.55" customHeight="1" s="25">
       <c r="A17" s="9" t="n">
         <v>12</v>
       </c>
@@ -2632,11 +2592,8 @@
       <c r="W17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="18" ht="13.55" customHeight="1" s="25">
       <c r="A18" s="9" t="n">
         <v>13</v>
       </c>
@@ -2708,11 +2665,8 @@
       <c r="W18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X18" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="19" ht="13.55" customHeight="1" s="25">
       <c r="A19" s="9" t="n">
         <v>14</v>
       </c>
@@ -2784,11 +2738,8 @@
       <c r="W19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X19" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="20" ht="13.55" customHeight="1" s="25">
       <c r="A20" s="9" t="n">
         <v>15</v>
       </c>
@@ -2860,11 +2811,8 @@
       <c r="W20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X20" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="21" ht="13.55" customHeight="1" s="25">
       <c r="A21" s="9" t="n">
         <v>16</v>
       </c>
@@ -2936,11 +2884,8 @@
       <c r="W21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X21" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="22" ht="13.55" customHeight="1" s="25">
       <c r="A22" s="9" t="n">
         <v>17</v>
       </c>
@@ -3012,11 +2957,8 @@
       <c r="W22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X22" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="23" ht="13.55" customHeight="1" s="25">
       <c r="A23" s="9" t="n">
         <v>18</v>
       </c>
@@ -3088,11 +3030,8 @@
       <c r="W23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X23" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="24" ht="13.55" customHeight="1" s="25">
       <c r="A24" s="9" t="n">
         <v>19</v>
       </c>
@@ -3164,11 +3103,8 @@
       <c r="W24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X24" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="25" ht="13.55" customHeight="1" s="25">
       <c r="A25" s="9" t="n">
         <v>20</v>
       </c>
@@ -3240,11 +3176,8 @@
       <c r="W25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X25" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="26.55" customHeight="1" s="24">
+    </row>
+    <row r="26" ht="26.55" customHeight="1" s="25">
       <c r="A26" s="9" t="n">
         <v>21</v>
       </c>
@@ -3317,11 +3250,8 @@
       <c r="W26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X26" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="27" ht="13.55" customHeight="1" s="25">
       <c r="A27" s="9" t="n">
         <v>22</v>
       </c>
@@ -3393,11 +3323,8 @@
       <c r="W27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X27" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="28" ht="13.55" customHeight="1" s="25">
       <c r="A28" s="9" t="n">
         <v>23</v>
       </c>
@@ -3469,11 +3396,8 @@
       <c r="W28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X28" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="29" ht="13.55" customHeight="1" s="25">
       <c r="A29" s="9" t="n">
         <v>24</v>
       </c>
@@ -3545,11 +3469,8 @@
       <c r="W29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X29" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="30" ht="13.55" customHeight="1" s="25">
       <c r="A30" s="9" t="n">
         <v>25</v>
       </c>
@@ -3621,11 +3542,8 @@
       <c r="W30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="31" ht="13.55" customHeight="1" s="25">
       <c r="A31" s="9" t="n">
         <v>26</v>
       </c>
@@ -3697,11 +3615,8 @@
       <c r="W31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X31" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="32" ht="13.55" customHeight="1" s="25">
       <c r="A32" s="9" t="n">
         <v>27</v>
       </c>
@@ -3773,11 +3688,8 @@
       <c r="W32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="33" ht="13.55" customHeight="1" s="25">
       <c r="A33" s="9" t="n">
         <v>28</v>
       </c>
@@ -3849,11 +3761,8 @@
       <c r="W33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X33" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="34" ht="13.55" customHeight="1" s="25">
       <c r="A34" s="9" t="n">
         <v>29</v>
       </c>
@@ -3925,11 +3834,8 @@
       <c r="W34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X34" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="35" ht="13.55" customHeight="1" s="25">
       <c r="A35" s="9" t="n">
         <v>30</v>
       </c>
@@ -4001,11 +3907,8 @@
       <c r="W35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X35" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="36" ht="13.55" customHeight="1" s="25">
       <c r="A36" s="9" t="n">
         <v>31</v>
       </c>
@@ -4077,11 +3980,8 @@
       <c r="W36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X36" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="37" ht="13.55" customHeight="1" s="25">
       <c r="A37" s="9" t="n">
         <v>32</v>
       </c>
@@ -4153,11 +4053,8 @@
       <c r="W37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X37" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="38" ht="13.55" customHeight="1" s="25">
       <c r="A38" s="9" t="n">
         <v>33</v>
       </c>
@@ -4229,11 +4126,8 @@
       <c r="W38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X38" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="39" ht="13.55" customHeight="1" s="25">
       <c r="A39" s="9" t="n">
         <v>34</v>
       </c>
@@ -4305,11 +4199,8 @@
       <c r="W39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X39" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="40" ht="13.55" customHeight="1" s="25">
       <c r="A40" s="9" t="n">
         <v>35</v>
       </c>
@@ -4381,11 +4272,8 @@
       <c r="W40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X40" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="41" ht="13.55" customHeight="1" s="25">
       <c r="A41" s="9" t="n">
         <v>36</v>
       </c>
@@ -4457,11 +4345,8 @@
       <c r="W41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X41" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="42" ht="13.55" customHeight="1" s="25">
       <c r="A42" s="9" t="n">
         <v>37</v>
       </c>
@@ -4533,11 +4418,8 @@
       <c r="W42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X42" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="43" ht="13.55" customHeight="1" s="25">
       <c r="A43" s="9" t="n">
         <v>38</v>
       </c>
@@ -4609,11 +4491,8 @@
       <c r="W43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X43" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="44" ht="13.55" customHeight="1" s="25">
       <c r="A44" s="9" t="n">
         <v>39</v>
       </c>
@@ -4685,11 +4564,8 @@
       <c r="W44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X44" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="45" ht="13.55" customHeight="1" s="25">
       <c r="A45" s="9" t="n">
         <v>40</v>
       </c>
@@ -4761,11 +4637,8 @@
       <c r="W45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X45" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="46" ht="13.55" customHeight="1" s="25">
       <c r="A46" s="9" t="n">
         <v>41</v>
       </c>
@@ -4837,11 +4710,8 @@
       <c r="W46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X46" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="47" ht="13.55" customHeight="1" s="25">
       <c r="A47" s="9" t="n">
         <v>42</v>
       </c>
@@ -4913,11 +4783,8 @@
       <c r="W47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X47" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="48" ht="13.55" customHeight="1" s="25">
       <c r="A48" s="9" t="n">
         <v>43</v>
       </c>
@@ -4989,11 +4856,8 @@
       <c r="W48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X48" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="49" ht="13.55" customHeight="1" s="25">
       <c r="A49" s="9" t="n">
         <v>44</v>
       </c>
@@ -5065,11 +4929,8 @@
       <c r="W49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X49" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="26.55" customHeight="1" s="24">
+    </row>
+    <row r="50" ht="26.55" customHeight="1" s="25">
       <c r="A50" s="9" t="n">
         <v>45</v>
       </c>
@@ -5142,11 +5003,8 @@
       <c r="W50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X50" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="26.55" customHeight="1" s="24">
+    </row>
+    <row r="51" ht="26.55" customHeight="1" s="25">
       <c r="A51" s="9" t="n">
         <v>46</v>
       </c>
@@ -5219,11 +5077,8 @@
       <c r="W51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X51" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="26.55" customHeight="1" s="24">
+    </row>
+    <row r="52" ht="26.55" customHeight="1" s="25">
       <c r="A52" s="9" t="n">
         <v>47</v>
       </c>
@@ -5296,11 +5151,8 @@
       <c r="W52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X52" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="26.55" customHeight="1" s="24">
+    </row>
+    <row r="53" ht="26.55" customHeight="1" s="25">
       <c r="A53" s="9" t="n">
         <v>48</v>
       </c>
@@ -5373,11 +5225,8 @@
       <c r="W53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X53" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="54" ht="13.55" customHeight="1" s="25">
       <c r="A54" s="9" t="n">
         <v>49</v>
       </c>
@@ -5449,11 +5298,8 @@
       <c r="W54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X54" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="55" ht="13.55" customHeight="1" s="25">
       <c r="A55" s="9" t="n">
         <v>50</v>
       </c>
@@ -5525,11 +5371,8 @@
       <c r="W55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X55" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="56" ht="13.55" customHeight="1" s="25">
       <c r="A56" s="9" t="n">
         <v>51</v>
       </c>
@@ -5601,11 +5444,8 @@
       <c r="W56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X56" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="57" ht="13.55" customHeight="1" s="25">
       <c r="A57" s="9" t="n">
         <v>52</v>
       </c>
@@ -5677,11 +5517,8 @@
       <c r="W57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X57" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="58" ht="13.55" customHeight="1" s="25">
       <c r="A58" s="9" t="n">
         <v>53</v>
       </c>
@@ -5753,11 +5590,8 @@
       <c r="W58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X58" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="59" ht="13.55" customHeight="1" s="25">
       <c r="A59" s="9" t="n">
         <v>54</v>
       </c>
@@ -5829,11 +5663,8 @@
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X59" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="60" ht="13.55" customHeight="1" s="25">
       <c r="A60" s="9" t="n">
         <v>55</v>
       </c>
@@ -5905,11 +5736,8 @@
       <c r="W60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X60" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="61" ht="13.55" customHeight="1" s="25">
       <c r="A61" s="9" t="n">
         <v>56</v>
       </c>
@@ -5981,11 +5809,8 @@
       <c r="W61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X61" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="62" ht="13.55" customHeight="1" s="25">
       <c r="A62" s="9" t="n">
         <v>57</v>
       </c>
@@ -6057,11 +5882,8 @@
       <c r="W62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X62" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="63" ht="13.55" customHeight="1" s="25">
       <c r="A63" s="9" t="n">
         <v>58</v>
       </c>
@@ -6133,11 +5955,8 @@
       <c r="W63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X63" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="64" ht="13.55" customHeight="1" s="25">
       <c r="A64" s="9" t="n">
         <v>59</v>
       </c>
@@ -6209,11 +6028,8 @@
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X64" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="65" ht="13.55" customHeight="1" s="25">
       <c r="A65" s="9" t="n">
         <v>60</v>
       </c>
@@ -6285,11 +6101,8 @@
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X65" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="66" ht="13.55" customHeight="1" s="25">
       <c r="A66" s="9" t="n">
         <v>61</v>
       </c>
@@ -6361,11 +6174,8 @@
       <c r="W66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X66" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="67" ht="13.55" customHeight="1" s="25">
       <c r="A67" s="9" t="n">
         <v>62</v>
       </c>
@@ -6437,11 +6247,8 @@
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X67" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="68" ht="13.55" customHeight="1" s="25">
       <c r="A68" s="9" t="n">
         <v>63</v>
       </c>
@@ -6513,11 +6320,8 @@
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="69" ht="13.55" customHeight="1" s="25">
       <c r="A69" s="9" t="n">
         <v>64</v>
       </c>
@@ -6589,11 +6393,8 @@
       <c r="W69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X69" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="70" ht="13.55" customHeight="1" s="25">
       <c r="A70" s="9" t="n">
         <v>65</v>
       </c>
@@ -6665,11 +6466,8 @@
       <c r="W70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X70" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="71" ht="13.55" customHeight="1" s="25">
       <c r="A71" s="9" t="n">
         <v>66</v>
       </c>
@@ -6741,11 +6539,8 @@
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X71" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="72" ht="13.55" customHeight="1" s="25">
       <c r="A72" s="9" t="n">
         <v>67</v>
       </c>
@@ -6817,11 +6612,8 @@
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="73" ht="13.55" customHeight="1" s="25">
       <c r="A73" s="9" t="n">
         <v>68</v>
       </c>
@@ -6893,11 +6685,8 @@
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X73" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" ht="26.55" customHeight="1" s="24">
+    </row>
+    <row r="74" ht="26.55" customHeight="1" s="25">
       <c r="A74" s="9" t="n">
         <v>69</v>
       </c>
@@ -6970,11 +6759,8 @@
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X74" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="75" ht="13.55" customHeight="1" s="25">
       <c r="A75" s="9" t="n">
         <v>70</v>
       </c>
@@ -7046,11 +6832,8 @@
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X75" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="76" ht="13.55" customHeight="1" s="25">
       <c r="A76" s="9" t="n">
         <v>71</v>
       </c>
@@ -7122,11 +6905,8 @@
       <c r="W76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X76" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="77" ht="13.55" customHeight="1" s="25">
       <c r="A77" s="9" t="n">
         <v>72</v>
       </c>
@@ -7198,11 +6978,8 @@
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X77" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="78" ht="13.55" customHeight="1" s="25">
       <c r="A78" s="9" t="n">
         <v>73</v>
       </c>
@@ -7274,11 +7051,8 @@
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X78" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" ht="26.55" customHeight="1" s="24">
+    </row>
+    <row r="79" ht="26.55" customHeight="1" s="25">
       <c r="A79" s="9" t="n">
         <v>74</v>
       </c>
@@ -7351,11 +7125,8 @@
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X79" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" ht="26.55" customHeight="1" s="24">
+    </row>
+    <row r="80" ht="26.55" customHeight="1" s="25">
       <c r="A80" s="9" t="n">
         <v>75</v>
       </c>
@@ -7428,11 +7199,8 @@
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="81" ht="13.55" customHeight="1" s="25">
       <c r="A81" s="9" t="n">
         <v>76</v>
       </c>
@@ -7504,11 +7272,8 @@
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X81" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="26.55" customHeight="1" s="24">
+    </row>
+    <row r="82" ht="26.55" customHeight="1" s="25">
       <c r="A82" s="9" t="n">
         <v>77</v>
       </c>
@@ -7581,11 +7346,8 @@
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="83" ht="13.55" customHeight="1" s="25">
       <c r="A83" s="9" t="n">
         <v>78</v>
       </c>
@@ -7657,11 +7419,8 @@
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="84" ht="13.55" customHeight="1" s="25">
       <c r="A84" s="9" t="n">
         <v>79</v>
       </c>
@@ -7733,11 +7492,8 @@
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="85" ht="13.55" customHeight="1" s="25">
       <c r="A85" s="9" t="n">
         <v>80</v>
       </c>
@@ -7809,11 +7565,8 @@
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="86" ht="13.55" customHeight="1" s="25">
       <c r="A86" s="9" t="n">
         <v>81</v>
       </c>
@@ -7885,11 +7638,8 @@
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X86" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="87" ht="13.55" customHeight="1" s="25">
       <c r="A87" s="9" t="n">
         <v>82</v>
       </c>
@@ -7961,11 +7711,8 @@
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="88" ht="13.55" customHeight="1" s="25">
       <c r="A88" s="9" t="n">
         <v>83</v>
       </c>
@@ -8037,13 +7784,12 @@
       <c r="W88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X88" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="13.55" customHeight="1" s="24">
-      <c r="A89" s="9" t="n">
-        <v>83</v>
+    </row>
+    <row r="89" ht="13.55" customHeight="1" s="25">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>83A</t>
+        </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
@@ -8113,11 +7859,8 @@
       <c r="W89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X89" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="90" ht="13.55" customHeight="1" s="25">
       <c r="A90" s="9" t="n">
         <v>84</v>
       </c>
@@ -8189,11 +7932,8 @@
       <c r="W90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X90" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="91" ht="13.55" customHeight="1" s="25">
       <c r="A91" s="9" t="n">
         <v>85</v>
       </c>
@@ -8265,11 +8005,8 @@
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="92" ht="13.55" customHeight="1" s="25">
       <c r="A92" s="9" t="n">
         <v>86</v>
       </c>
@@ -8341,11 +8078,8 @@
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="93" ht="13.55" customHeight="1" s="25">
       <c r="A93" s="9" t="n">
         <v>87</v>
       </c>
@@ -8417,11 +8151,8 @@
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X93" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="94" ht="13.55" customHeight="1" s="25">
       <c r="A94" s="9" t="n">
         <v>88</v>
       </c>
@@ -8493,11 +8224,8 @@
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X94" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="95" ht="13.55" customHeight="1" s="25">
       <c r="A95" s="9" t="n">
         <v>89</v>
       </c>
@@ -8569,11 +8297,8 @@
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X95" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="96" ht="13.55" customHeight="1" s="25">
       <c r="A96" s="9" t="n">
         <v>90</v>
       </c>
@@ -8645,11 +8370,8 @@
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X96" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="97" ht="13.55" customHeight="1" s="25">
       <c r="A97" s="9" t="n">
         <v>91</v>
       </c>
@@ -8721,11 +8443,8 @@
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="98" ht="13.55" customHeight="1" s="25">
       <c r="A98" s="9" t="n">
         <v>92</v>
       </c>
@@ -8797,11 +8516,8 @@
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="99" ht="13.55" customHeight="1" s="25">
       <c r="A99" s="9" t="n">
         <v>93</v>
       </c>
@@ -8873,11 +8589,8 @@
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X99" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="100" ht="13.55" customHeight="1" s="25">
       <c r="A100" s="9" t="n">
         <v>94</v>
       </c>
@@ -8949,11 +8662,8 @@
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="101" ht="13.55" customHeight="1" s="25">
       <c r="A101" s="9" t="n">
         <v>95</v>
       </c>
@@ -9025,11 +8735,8 @@
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="102" ht="13.55" customHeight="1" s="25">
       <c r="A102" s="9" t="n">
         <v>96</v>
       </c>
@@ -9101,11 +8808,8 @@
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="103" ht="13.55" customHeight="1" s="25">
       <c r="A103" s="9" t="n">
         <v>97</v>
       </c>
@@ -9177,11 +8881,8 @@
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="104" ht="13.55" customHeight="1" s="25">
       <c r="A104" s="9" t="n">
         <v>98</v>
       </c>
@@ -9253,11 +8954,8 @@
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="105" ht="13.55" customHeight="1" s="25">
       <c r="A105" s="9" t="n">
         <v>99</v>
       </c>
@@ -9329,11 +9027,8 @@
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="106" ht="13.55" customHeight="1" s="25">
       <c r="A106" s="9" t="n">
         <v>100</v>
       </c>
@@ -9405,11 +9100,8 @@
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="107" ht="13.55" customHeight="1" s="25">
       <c r="A107" s="9" t="n">
         <v>101</v>
       </c>
@@ -9481,11 +9173,8 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="108" ht="13.55" customHeight="1" s="25">
       <c r="A108" s="9" t="n">
         <v>102</v>
       </c>
@@ -9557,11 +9246,8 @@
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="109" ht="13.55" customHeight="1" s="25">
       <c r="A109" s="9" t="n">
         <v>103</v>
       </c>
@@ -9633,11 +9319,8 @@
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X109" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="110" ht="13.55" customHeight="1" s="25">
       <c r="A110" s="9" t="n">
         <v>104</v>
       </c>
@@ -9709,11 +9392,8 @@
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="111" ht="13.55" customHeight="1" s="25">
       <c r="A111" s="9" t="n">
         <v>105</v>
       </c>
@@ -9785,11 +9465,8 @@
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="112" ht="13.55" customHeight="1" s="25">
       <c r="A112" s="9" t="n">
         <v>106</v>
       </c>
@@ -9861,11 +9538,8 @@
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X112" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="113" ht="13.55" customHeight="1" s="25">
       <c r="A113" s="9" t="n">
         <v>107</v>
       </c>
@@ -9937,11 +9611,8 @@
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="114" ht="13.55" customHeight="1" s="25">
       <c r="A114" s="9" t="n">
         <v>108</v>
       </c>
@@ -10013,11 +9684,8 @@
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X114" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="115" ht="13.55" customHeight="1" s="25">
       <c r="A115" s="9" t="n">
         <v>109</v>
       </c>
@@ -10089,11 +9757,8 @@
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X115" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="116" ht="13.55" customHeight="1" s="25">
       <c r="A116" s="9" t="n">
         <v>110</v>
       </c>
@@ -10165,11 +9830,8 @@
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="117" ht="13.55" customHeight="1" s="25">
       <c r="A117" s="9" t="n">
         <v>111</v>
       </c>
@@ -10241,11 +9903,8 @@
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X117" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="118" ht="13.55" customHeight="1" s="25">
       <c r="A118" s="9" t="n">
         <v>112</v>
       </c>
@@ -10317,11 +9976,8 @@
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="119" ht="13.55" customHeight="1" s="25">
       <c r="A119" s="9" t="n">
         <v>113</v>
       </c>
@@ -10393,11 +10049,8 @@
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="120" ht="13.55" customHeight="1" s="25">
       <c r="A120" s="9" t="n">
         <v>114</v>
       </c>
@@ -10469,11 +10122,8 @@
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="121" ht="13.55" customHeight="1" s="25">
       <c r="A121" s="9" t="n">
         <v>115</v>
       </c>
@@ -10545,11 +10195,8 @@
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X121" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="122" ht="13.55" customHeight="1" s="25">
       <c r="A122" s="9" t="n">
         <v>116</v>
       </c>
@@ -10621,11 +10268,8 @@
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="123" ht="13.55" customHeight="1" s="25">
       <c r="A123" s="9" t="n">
         <v>117</v>
       </c>
@@ -10697,11 +10341,8 @@
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="124" ht="13.55" customHeight="1" s="25">
       <c r="A124" s="9" t="n">
         <v>118</v>
       </c>
@@ -10773,11 +10414,8 @@
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="125" ht="13.55" customHeight="1" s="25">
       <c r="A125" s="9" t="n">
         <v>119</v>
       </c>
@@ -10849,11 +10487,8 @@
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X125" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="126" ht="13.55" customHeight="1" s="25">
       <c r="A126" s="9" t="n">
         <v>120</v>
       </c>
@@ -10925,11 +10560,8 @@
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="127" ht="13.55" customHeight="1" s="25">
       <c r="A127" s="9" t="n">
         <v>121</v>
       </c>
@@ -11001,11 +10633,8 @@
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X127" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="128" ht="13.55" customHeight="1" s="25">
       <c r="A128" s="9" t="n">
         <v>122</v>
       </c>
@@ -11077,11 +10706,8 @@
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X128" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="129" ht="13.55" customHeight="1" s="25">
       <c r="A129" s="9" t="n">
         <v>123</v>
       </c>
@@ -11153,11 +10779,8 @@
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="130" ht="13.55" customHeight="1" s="25">
       <c r="A130" s="9" t="n">
         <v>124</v>
       </c>
@@ -11229,11 +10852,8 @@
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="131" ht="13.55" customHeight="1" s="25">
       <c r="A131" s="9" t="n">
         <v>125</v>
       </c>
@@ -11305,11 +10925,8 @@
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="132" ht="13.55" customHeight="1" s="25">
       <c r="A132" s="9" t="n">
         <v>126</v>
       </c>
@@ -11381,11 +10998,8 @@
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X132" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="133" ht="13.55" customHeight="1" s="25">
       <c r="A133" s="9" t="n">
         <v>127</v>
       </c>
@@ -11457,11 +11071,8 @@
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X133" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="134" ht="13.55" customHeight="1" s="25">
       <c r="A134" s="9" t="n">
         <v>128</v>
       </c>
@@ -11533,11 +11144,8 @@
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X134" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="135" ht="13.55" customHeight="1" s="25">
       <c r="A135" s="9" t="n">
         <v>129</v>
       </c>
@@ -11609,11 +11217,8 @@
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X135" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="136" ht="13.55" customHeight="1" s="25">
       <c r="A136" s="9" t="n">
         <v>130</v>
       </c>
@@ -11685,11 +11290,8 @@
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X136" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="137" ht="13.55" customHeight="1" s="25">
       <c r="A137" s="9" t="n">
         <v>131</v>
       </c>
@@ -11761,11 +11363,8 @@
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X137" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="138" ht="13.55" customHeight="1" s="25">
       <c r="A138" s="9" t="n">
         <v>132</v>
       </c>
@@ -11837,11 +11436,8 @@
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X138" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="139" ht="13.55" customHeight="1" s="25">
       <c r="A139" s="9" t="n">
         <v>133</v>
       </c>
@@ -11913,11 +11509,8 @@
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X139" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="140" ht="13.55" customHeight="1" s="25">
       <c r="A140" s="9" t="n">
         <v>134</v>
       </c>
@@ -11989,11 +11582,8 @@
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X140" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="141" ht="13.55" customHeight="1" s="25">
       <c r="A141" s="9" t="n">
         <v>135</v>
       </c>
@@ -12065,11 +11655,8 @@
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X141" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="142" ht="13.55" customHeight="1" s="25">
       <c r="A142" s="9" t="n">
         <v>136</v>
       </c>
@@ -12141,11 +11728,8 @@
       <c r="W142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X142" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="143" ht="13.55" customHeight="1" s="25">
       <c r="A143" s="9" t="n">
         <v>137</v>
       </c>
@@ -12217,11 +11801,8 @@
       <c r="W143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X143" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="144" ht="13.55" customHeight="1" s="25">
       <c r="A144" s="9" t="n">
         <v>138</v>
       </c>
@@ -12293,11 +11874,8 @@
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X144" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="145" ht="13.55" customHeight="1" s="25">
       <c r="A145" s="9" t="n">
         <v>139</v>
       </c>
@@ -12369,11 +11947,8 @@
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X145" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="146" ht="13.55" customHeight="1" s="25">
       <c r="A146" s="9" t="n">
         <v>140</v>
       </c>
@@ -12445,11 +12020,8 @@
       <c r="W146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X146" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="147" ht="13.55" customHeight="1" s="25">
       <c r="A147" s="9" t="n">
         <v>141</v>
       </c>
@@ -12521,11 +12093,8 @@
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X147" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="148" ht="13.55" customHeight="1" s="25">
       <c r="A148" s="9" t="n">
         <v>142</v>
       </c>
@@ -12597,11 +12166,8 @@
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X148" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="149" ht="13.55" customHeight="1" s="25">
       <c r="A149" s="9" t="n">
         <v>143</v>
       </c>
@@ -12673,11 +12239,8 @@
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X149" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="150" ht="13.55" customHeight="1" s="25">
       <c r="A150" s="9" t="n">
         <v>144</v>
       </c>
@@ -12749,11 +12312,8 @@
       <c r="W150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X150" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="151" ht="13.55" customHeight="1" s="25">
       <c r="A151" s="9" t="n">
         <v>145</v>
       </c>
@@ -12825,11 +12385,8 @@
       <c r="W151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X151" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="152" ht="13.55" customHeight="1" s="25">
       <c r="A152" s="9" t="n">
         <v>146</v>
       </c>
@@ -12901,11 +12458,8 @@
       <c r="W152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X152" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="153" ht="13.55" customHeight="1" s="25">
       <c r="A153" s="9" t="n">
         <v>147</v>
       </c>
@@ -12977,11 +12531,8 @@
       <c r="W153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X153" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="154" ht="13.55" customHeight="1" s="25">
       <c r="A154" s="9" t="n">
         <v>148</v>
       </c>
@@ -13053,11 +12604,8 @@
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X154" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="155" ht="13.55" customHeight="1" s="25">
       <c r="A155" s="9" t="n">
         <v>149</v>
       </c>
@@ -13129,11 +12677,8 @@
       <c r="W155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X155" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="156" ht="13.55" customHeight="1" s="25">
       <c r="A156" s="9" t="n">
         <v>150</v>
       </c>
@@ -13205,11 +12750,8 @@
       <c r="W156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X156" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="157" ht="13.55" customHeight="1" s="25">
       <c r="A157" s="9" t="n">
         <v>151</v>
       </c>
@@ -13281,11 +12823,8 @@
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X157" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="158" ht="13.55" customHeight="1" s="25">
       <c r="A158" s="9" t="n">
         <v>152</v>
       </c>
@@ -13357,11 +12896,8 @@
       <c r="W158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X158" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="159" ht="13.55" customHeight="1" s="25">
       <c r="A159" s="9" t="n">
         <v>153</v>
       </c>
@@ -13433,11 +12969,8 @@
       <c r="W159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X159" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="160" ht="13.55" customHeight="1" s="25">
       <c r="A160" s="9" t="n">
         <v>154</v>
       </c>
@@ -13509,11 +13042,8 @@
       <c r="W160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X160" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="161" ht="13.55" customHeight="1" s="25">
       <c r="A161" s="9" t="n">
         <v>155</v>
       </c>
@@ -13585,11 +13115,8 @@
       <c r="W161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X161" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="162" ht="13.55" customHeight="1" s="25">
       <c r="A162" s="9" t="n">
         <v>156</v>
       </c>
@@ -13661,11 +13188,8 @@
       <c r="W162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X162" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="163" ht="13.55" customHeight="1" s="25">
       <c r="A163" s="9" t="n">
         <v>157</v>
       </c>
@@ -13737,11 +13261,8 @@
       <c r="W163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X163" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="164" ht="13.55" customHeight="1" s="25">
       <c r="A164" s="9" t="n">
         <v>158</v>
       </c>
@@ -13813,11 +13334,8 @@
       <c r="W164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X164" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="165" ht="13.55" customHeight="1" s="25">
       <c r="A165" s="9" t="n">
         <v>159</v>
       </c>
@@ -13889,11 +13407,8 @@
       <c r="W165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X165" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="166" ht="13.55" customHeight="1" s="25">
       <c r="A166" s="9" t="n">
         <v>160</v>
       </c>
@@ -13965,11 +13480,8 @@
       <c r="W166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X166" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="167" ht="13.55" customHeight="1" s="25">
       <c r="A167" s="9" t="n">
         <v>161</v>
       </c>
@@ -14041,11 +13553,8 @@
       <c r="W167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X167" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="168" ht="13.55" customHeight="1" s="25">
       <c r="A168" s="9" t="n">
         <v>162</v>
       </c>
@@ -14117,11 +13626,8 @@
       <c r="W168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X168" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="169" ht="13.55" customHeight="1" s="25">
       <c r="A169" s="9" t="n">
         <v>163</v>
       </c>
@@ -14193,11 +13699,8 @@
       <c r="W169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X169" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="170" ht="13.55" customHeight="1" s="25">
       <c r="A170" s="9" t="n">
         <v>164</v>
       </c>
@@ -14269,11 +13772,8 @@
       <c r="W170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X170" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="171" ht="13.55" customHeight="1" s="25">
       <c r="A171" s="9" t="n">
         <v>165</v>
       </c>
@@ -14345,11 +13845,8 @@
       <c r="W171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X171" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="172" ht="13.55" customHeight="1" s="25">
       <c r="A172" s="9" t="n">
         <v>166</v>
       </c>
@@ -14421,11 +13918,8 @@
       <c r="W172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X172" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="173" ht="13.55" customHeight="1" s="25">
       <c r="A173" s="9" t="n">
         <v>167</v>
       </c>
@@ -14497,11 +13991,8 @@
       <c r="W173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X173" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="174" ht="13.55" customHeight="1" s="25">
       <c r="A174" s="9" t="n">
         <v>168</v>
       </c>
@@ -14573,11 +14064,8 @@
       <c r="W174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X174" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="175" ht="13.55" customHeight="1" s="25">
       <c r="A175" s="9" t="n">
         <v>169</v>
       </c>
@@ -14649,11 +14137,8 @@
       <c r="W175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X175" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="176" ht="13.55" customHeight="1" s="25">
       <c r="A176" s="9" t="n">
         <v>170</v>
       </c>
@@ -14725,11 +14210,8 @@
       <c r="W176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X176" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="177" ht="13.55" customHeight="1" s="25">
       <c r="A177" s="9" t="n">
         <v>171</v>
       </c>
@@ -14801,11 +14283,8 @@
       <c r="W177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X177" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="178" ht="13.55" customHeight="1" s="25">
       <c r="A178" s="9" t="n">
         <v>172</v>
       </c>
@@ -14877,11 +14356,8 @@
       <c r="W178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X178" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="179" ht="13.55" customHeight="1" s="25">
       <c r="A179" s="9" t="n">
         <v>173</v>
       </c>
@@ -14953,11 +14429,8 @@
       <c r="W179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X179" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="180" ht="13.55" customHeight="1" s="25">
       <c r="A180" s="9" t="n">
         <v>174</v>
       </c>
@@ -15029,11 +14502,8 @@
       <c r="W180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X180" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="181" ht="13.55" customHeight="1" s="25">
       <c r="A181" s="9" t="n">
         <v>175</v>
       </c>
@@ -15105,11 +14575,8 @@
       <c r="W181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X181" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="182" ht="13.55" customHeight="1" s="25">
       <c r="A182" s="9" t="n">
         <v>176</v>
       </c>
@@ -15181,11 +14648,8 @@
       <c r="W182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X182" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="183" ht="13.55" customHeight="1" s="25">
       <c r="A183" s="9" t="n">
         <v>177</v>
       </c>
@@ -15257,11 +14721,8 @@
       <c r="W183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X183" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="184" ht="13.55" customHeight="1" s="25">
       <c r="A184" s="9" t="n">
         <v>178</v>
       </c>
@@ -15333,11 +14794,8 @@
       <c r="W184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X184" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="185" ht="13.55" customHeight="1" s="25">
       <c r="A185" s="9" t="n">
         <v>179</v>
       </c>
@@ -15409,11 +14867,8 @@
       <c r="W185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X185" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="186" ht="13.55" customHeight="1" s="25">
       <c r="A186" s="9" t="n">
         <v>180</v>
       </c>
@@ -15485,11 +14940,8 @@
       <c r="W186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X186" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="187" ht="13.55" customHeight="1" s="25">
       <c r="A187" s="9" t="n">
         <v>181</v>
       </c>
@@ -15561,11 +15013,8 @@
       <c r="W187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X187" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="188" ht="13.55" customHeight="1" s="25">
       <c r="A188" s="9" t="n">
         <v>182</v>
       </c>
@@ -15637,11 +15086,8 @@
       <c r="W188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X188" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="189" ht="13.55" customHeight="1" s="25">
       <c r="A189" s="9" t="n">
         <v>183</v>
       </c>
@@ -15713,11 +15159,8 @@
       <c r="W189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X189" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="190" ht="13.55" customHeight="1" s="25">
       <c r="A190" s="9" t="n">
         <v>184</v>
       </c>
@@ -15789,11 +15232,8 @@
       <c r="W190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X190" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="191" ht="13.55" customHeight="1" s="25">
       <c r="A191" s="9" t="n">
         <v>185</v>
       </c>
@@ -15865,11 +15305,8 @@
       <c r="W191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X191" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="192" ht="13.55" customHeight="1" s="25">
       <c r="A192" s="9" t="n">
         <v>186</v>
       </c>
@@ -15941,11 +15378,8 @@
       <c r="W192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X192" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="193" ht="13.55" customHeight="1" s="25">
       <c r="A193" s="9" t="n">
         <v>187</v>
       </c>
@@ -16017,11 +15451,8 @@
       <c r="W193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X193" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="194" ht="13.55" customHeight="1" s="25">
       <c r="A194" s="9" t="n">
         <v>188</v>
       </c>
@@ -16093,11 +15524,8 @@
       <c r="W194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X194" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="195" ht="13.55" customHeight="1" s="25">
       <c r="A195" s="9" t="n">
         <v>189</v>
       </c>
@@ -16169,11 +15597,8 @@
       <c r="W195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X195" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="196" ht="13.55" customHeight="1" s="25">
       <c r="A196" s="9" t="n">
         <v>190</v>
       </c>
@@ -16245,11 +15670,8 @@
       <c r="W196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X196" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="197" ht="13.55" customHeight="1" s="25">
       <c r="A197" s="9" t="n">
         <v>191</v>
       </c>
@@ -16321,11 +15743,8 @@
       <c r="W197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X197" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="198" ht="13.55" customHeight="1" s="25">
       <c r="A198" s="9" t="n">
         <v>192</v>
       </c>
@@ -16397,11 +15816,8 @@
       <c r="W198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X198" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="199" ht="13.55" customHeight="1" s="25">
       <c r="A199" s="9" t="n">
         <v>193</v>
       </c>
@@ -16473,11 +15889,8 @@
       <c r="W199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X199" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="200" ht="13.55" customHeight="1" s="25">
       <c r="A200" s="9" t="n">
         <v>194</v>
       </c>
@@ -16549,11 +15962,8 @@
       <c r="W200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X200" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="201" ht="13.55" customHeight="1" s="25">
       <c r="A201" s="9" t="n">
         <v>195</v>
       </c>
@@ -16625,11 +16035,8 @@
       <c r="W201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X201" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="202" ht="13.55" customHeight="1" s="25">
       <c r="A202" s="9" t="n">
         <v>196</v>
       </c>
@@ -16701,11 +16108,8 @@
       <c r="W202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X202" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="203" ht="13.55" customHeight="1" s="25">
       <c r="A203" s="9" t="n">
         <v>197</v>
       </c>
@@ -16777,11 +16181,8 @@
       <c r="W203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X203" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="204" ht="13.55" customHeight="1" s="25">
       <c r="A204" s="9" t="n">
         <v>198</v>
       </c>
@@ -16853,11 +16254,8 @@
       <c r="W204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X204" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="205" ht="13.55" customHeight="1" s="25">
       <c r="A205" s="9" t="n">
         <v>199</v>
       </c>
@@ -16929,11 +16327,8 @@
       <c r="W205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X205" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="206" ht="13.55" customHeight="1" s="25">
       <c r="A206" s="9" t="n">
         <v>200</v>
       </c>
@@ -17005,11 +16400,8 @@
       <c r="W206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X206" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="207" ht="13.55" customHeight="1" s="25">
       <c r="A207" s="9" t="n">
         <v>201</v>
       </c>
@@ -17081,11 +16473,8 @@
       <c r="W207" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X207" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="208" ht="13.55" customHeight="1" s="25">
       <c r="A208" s="9" t="n">
         <v>202</v>
       </c>
@@ -17157,11 +16546,8 @@
       <c r="W208" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X208" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="209" ht="13.55" customHeight="1" s="25">
       <c r="A209" s="9" t="n">
         <v>203</v>
       </c>
@@ -17233,11 +16619,8 @@
       <c r="W209" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X209" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="210" ht="13.55" customHeight="1" s="25">
       <c r="A210" s="9" t="n">
         <v>204</v>
       </c>
@@ -17309,11 +16692,8 @@
       <c r="W210" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X210" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="211" ht="13.55" customHeight="1" s="25">
       <c r="A211" s="9" t="n">
         <v>205</v>
       </c>
@@ -17385,11 +16765,8 @@
       <c r="W211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X211" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="212" ht="13.55" customHeight="1" s="25">
       <c r="A212" s="9" t="n">
         <v>206</v>
       </c>
@@ -17461,11 +16838,8 @@
       <c r="W212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X212" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="213" ht="13.55" customHeight="1" s="25">
       <c r="A213" s="9" t="n">
         <v>207</v>
       </c>
@@ -17537,11 +16911,8 @@
       <c r="W213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X213" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="214" ht="13.55" customHeight="1" s="25">
       <c r="A214" s="9" t="n">
         <v>208</v>
       </c>
@@ -17613,11 +16984,8 @@
       <c r="W214" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X214" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="215" ht="13.55" customHeight="1" s="25">
       <c r="A215" s="9" t="n">
         <v>209</v>
       </c>
@@ -17689,11 +17057,8 @@
       <c r="W215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X215" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="216" ht="13.55" customHeight="1" s="25">
       <c r="A216" s="9" t="n">
         <v>210</v>
       </c>
@@ -17765,11 +17130,8 @@
       <c r="W216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X216" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="217" ht="13.55" customHeight="1" s="25">
       <c r="A217" s="9" t="n">
         <v>211</v>
       </c>
@@ -17841,11 +17203,8 @@
       <c r="W217" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X217" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="218" ht="13.55" customHeight="1" s="25">
       <c r="A218" s="9" t="n">
         <v>212</v>
       </c>
@@ -17917,11 +17276,8 @@
       <c r="W218" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X218" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="219" ht="13.55" customHeight="1" s="25">
       <c r="A219" s="9" t="n">
         <v>213</v>
       </c>
@@ -17993,11 +17349,8 @@
       <c r="W219" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X219" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="220" ht="13.55" customHeight="1" s="25">
       <c r="A220" s="9" t="n">
         <v>214</v>
       </c>
@@ -18069,11 +17422,8 @@
       <c r="W220" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X220" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="221" ht="13.55" customHeight="1" s="25">
       <c r="A221" s="9" t="n">
         <v>215</v>
       </c>
@@ -18145,11 +17495,8 @@
       <c r="W221" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X221" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="222" ht="13.55" customHeight="1" s="25">
       <c r="A222" s="9" t="n">
         <v>216</v>
       </c>
@@ -18221,11 +17568,8 @@
       <c r="W222" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X222" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="223" ht="13.55" customHeight="1" s="25">
       <c r="A223" s="9" t="n">
         <v>217</v>
       </c>
@@ -18297,11 +17641,8 @@
       <c r="W223" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X223" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="224" ht="13.55" customHeight="1" s="25">
       <c r="A224" s="9" t="n">
         <v>218</v>
       </c>
@@ -18373,11 +17714,8 @@
       <c r="W224" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X224" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="225" ht="13.55" customHeight="1" s="25">
       <c r="A225" s="9" t="n">
         <v>219</v>
       </c>
@@ -18449,11 +17787,8 @@
       <c r="W225" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X225" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="226" ht="13.55" customHeight="1" s="25">
       <c r="A226" s="9" t="n">
         <v>220</v>
       </c>
@@ -18525,11 +17860,8 @@
       <c r="W226" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X226" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="227" ht="13.55" customHeight="1" s="25">
       <c r="A227" s="9" t="n">
         <v>221</v>
       </c>
@@ -18601,11 +17933,8 @@
       <c r="W227" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X227" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="228" ht="13.55" customHeight="1" s="25">
       <c r="A228" s="9" t="n">
         <v>222</v>
       </c>
@@ -18677,11 +18006,8 @@
       <c r="W228" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X228" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="229" ht="13.55" customHeight="1" s="25">
       <c r="A229" s="9" t="n">
         <v>223</v>
       </c>
@@ -18753,11 +18079,8 @@
       <c r="W229" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X229" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="230" ht="13.55" customHeight="1" s="25">
       <c r="A230" s="9" t="n">
         <v>224</v>
       </c>
@@ -18829,11 +18152,8 @@
       <c r="W230" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X230" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="231" ht="13.55" customHeight="1" s="25">
       <c r="A231" s="9" t="n">
         <v>225</v>
       </c>
@@ -18905,11 +18225,8 @@
       <c r="W231" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X231" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="232" ht="13.55" customHeight="1" s="25">
       <c r="A232" s="9" t="n">
         <v>226</v>
       </c>
@@ -18981,11 +18298,8 @@
       <c r="W232" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X232" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="233" ht="13.55" customHeight="1" s="25">
       <c r="A233" s="9" t="n">
         <v>227</v>
       </c>
@@ -19057,11 +18371,8 @@
       <c r="W233" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X233" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="234" ht="13.55" customHeight="1" s="25">
       <c r="A234" s="9" t="n">
         <v>228</v>
       </c>
@@ -19133,11 +18444,8 @@
       <c r="W234" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X234" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="235" ht="13.55" customHeight="1" s="25">
       <c r="A235" s="9" t="n">
         <v>229</v>
       </c>
@@ -19209,11 +18517,8 @@
       <c r="W235" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X235" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="236" ht="13.55" customHeight="1" s="25">
       <c r="A236" s="9" t="n">
         <v>230</v>
       </c>
@@ -19285,11 +18590,8 @@
       <c r="W236" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X236" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="237" ht="13.55" customHeight="1" s="25">
       <c r="A237" s="9" t="n">
         <v>231</v>
       </c>
@@ -19361,11 +18663,8 @@
       <c r="W237" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X237" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="238" ht="13.55" customHeight="1" s="25">
       <c r="A238" s="9" t="n">
         <v>232</v>
       </c>
@@ -19437,11 +18736,8 @@
       <c r="W238" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X238" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="239" ht="13.55" customHeight="1" s="25">
       <c r="A239" s="9" t="n">
         <v>233</v>
       </c>
@@ -19513,11 +18809,8 @@
       <c r="W239" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X239" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="240" ht="13.55" customHeight="1" s="25">
       <c r="A240" s="9" t="n">
         <v>234</v>
       </c>
@@ -19589,11 +18882,8 @@
       <c r="W240" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X240" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="241" ht="13.55" customHeight="1" s="25">
       <c r="A241" s="9" t="n">
         <v>235</v>
       </c>
@@ -19665,11 +18955,8 @@
       <c r="W241" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X241" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="242" ht="13.55" customHeight="1" s="25">
       <c r="A242" s="9" t="n">
         <v>236</v>
       </c>
@@ -19741,11 +19028,8 @@
       <c r="W242" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X242" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="243" ht="13.55" customHeight="1" s="25">
       <c r="A243" s="9" t="n">
         <v>237</v>
       </c>
@@ -19817,11 +19101,8 @@
       <c r="W243" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X243" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="244" ht="13.55" customHeight="1" s="25">
       <c r="A244" s="9" t="n">
         <v>238</v>
       </c>
@@ -19893,11 +19174,8 @@
       <c r="W244" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X244" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="245" ht="13.55" customHeight="1" s="25">
       <c r="A245" s="9" t="n">
         <v>239</v>
       </c>
@@ -19969,11 +19247,8 @@
       <c r="W245" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X245" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="246" ht="13.55" customHeight="1" s="25">
       <c r="A246" s="9" t="n">
         <v>240</v>
       </c>
@@ -20045,11 +19320,8 @@
       <c r="W246" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X246" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="247" ht="13.55" customHeight="1" s="25">
       <c r="A247" s="9" t="n">
         <v>241</v>
       </c>
@@ -20121,11 +19393,8 @@
       <c r="W247" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X247" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="248" ht="13.55" customHeight="1" s="25">
       <c r="A248" s="9" t="n">
         <v>242</v>
       </c>
@@ -20197,11 +19466,8 @@
       <c r="W248" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X248" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="249" ht="13.55" customHeight="1" s="25">
       <c r="A249" s="9" t="n">
         <v>243</v>
       </c>
@@ -20273,11 +19539,8 @@
       <c r="W249" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X249" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="250" ht="13.55" customHeight="1" s="25">
       <c r="A250" s="9" t="n">
         <v>244</v>
       </c>
@@ -20349,11 +19612,8 @@
       <c r="W250" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X250" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="251" ht="13.55" customHeight="1" s="25">
       <c r="A251" s="9" t="n">
         <v>245</v>
       </c>
@@ -20425,11 +19685,8 @@
       <c r="W251" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X251" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="252" ht="13.55" customHeight="1" s="25">
       <c r="A252" s="9" t="n">
         <v>246</v>
       </c>
@@ -20501,11 +19758,8 @@
       <c r="W252" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X252" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="253" ht="13.55" customHeight="1" s="25">
       <c r="A253" s="9" t="n">
         <v>247</v>
       </c>
@@ -20577,11 +19831,8 @@
       <c r="W253" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X253" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="254" ht="13.55" customHeight="1" s="25">
       <c r="A254" s="9" t="n">
         <v>248</v>
       </c>
@@ -20653,11 +19904,8 @@
       <c r="W254" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X254" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="255" ht="13.55" customHeight="1" s="25">
       <c r="A255" s="9" t="n">
         <v>249</v>
       </c>
@@ -20729,11 +19977,8 @@
       <c r="W255" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X255" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="256" ht="13.55" customHeight="1" s="25">
       <c r="A256" s="9" t="n">
         <v>250</v>
       </c>
@@ -20805,11 +20050,8 @@
       <c r="W256" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X256" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="257" ht="13.55" customHeight="1" s="25">
       <c r="A257" s="9" t="n">
         <v>251</v>
       </c>
@@ -20881,11 +20123,8 @@
       <c r="W257" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X257" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="258" ht="13.55" customHeight="1" s="25">
       <c r="A258" s="9" t="n">
         <v>252</v>
       </c>
@@ -20957,11 +20196,8 @@
       <c r="W258" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X258" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="259" ht="13.55" customHeight="1" s="25">
       <c r="A259" s="9" t="n">
         <v>253</v>
       </c>
@@ -21033,11 +20269,8 @@
       <c r="W259" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X259" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="260" ht="13.55" customHeight="1" s="25">
       <c r="A260" s="9" t="n">
         <v>254</v>
       </c>
@@ -21109,11 +20342,8 @@
       <c r="W260" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X260" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="261" ht="13.55" customHeight="1" s="25">
       <c r="A261" s="9" t="n">
         <v>255</v>
       </c>
@@ -21185,11 +20415,8 @@
       <c r="W261" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X261" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="262" ht="13.55" customHeight="1" s="25">
       <c r="A262" s="9" t="n">
         <v>256</v>
       </c>
@@ -21261,11 +20488,8 @@
       <c r="W262" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X262" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="263" ht="13.55" customHeight="1" s="25">
       <c r="A263" s="9" t="n">
         <v>257</v>
       </c>
@@ -21337,11 +20561,8 @@
       <c r="W263" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X263" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="264" ht="13.55" customHeight="1" s="25">
       <c r="A264" s="9" t="n">
         <v>258</v>
       </c>
@@ -21413,11 +20634,8 @@
       <c r="W264" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X264" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="265" ht="13.55" customHeight="1" s="25">
       <c r="A265" s="9" t="n">
         <v>259</v>
       </c>
@@ -21489,11 +20707,8 @@
       <c r="W265" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X265" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="266" ht="13.55" customHeight="1" s="25">
       <c r="A266" s="9" t="n">
         <v>260</v>
       </c>
@@ -21565,11 +20780,8 @@
       <c r="W266" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X266" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="267" ht="13.55" customHeight="1" s="25">
       <c r="A267" s="9" t="n">
         <v>261</v>
       </c>
@@ -21641,11 +20853,8 @@
       <c r="W267" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X267" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="268" ht="13.55" customHeight="1" s="25">
       <c r="A268" s="9" t="n">
         <v>262</v>
       </c>
@@ -21717,11 +20926,8 @@
       <c r="W268" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X268" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="269" ht="13.55" customHeight="1" s="25">
       <c r="A269" s="9" t="n">
         <v>263</v>
       </c>
@@ -21793,11 +20999,8 @@
       <c r="W269" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X269" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="270" ht="13.55" customHeight="1" s="25">
       <c r="A270" s="9" t="n">
         <v>264</v>
       </c>
@@ -21869,11 +21072,8 @@
       <c r="W270" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X270" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="271" ht="13.55" customHeight="1" s="25">
       <c r="A271" s="9" t="n">
         <v>265</v>
       </c>
@@ -21945,11 +21145,8 @@
       <c r="W271" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X271" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="272" ht="13.55" customHeight="1" s="25">
       <c r="A272" s="9" t="n">
         <v>266</v>
       </c>
@@ -22021,11 +21218,8 @@
       <c r="W272" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X272" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="273" ht="13.55" customHeight="1" s="25">
       <c r="A273" s="9" t="n">
         <v>267</v>
       </c>
@@ -22097,11 +21291,8 @@
       <c r="W273" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X273" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="274" ht="13.55" customHeight="1" s="25">
       <c r="A274" s="9" t="n">
         <v>268</v>
       </c>
@@ -22173,11 +21364,8 @@
       <c r="W274" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X274" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="275" ht="13.55" customHeight="1" s="25">
       <c r="A275" s="9" t="n">
         <v>269</v>
       </c>
@@ -22249,11 +21437,8 @@
       <c r="W275" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X275" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="276" ht="13.55" customHeight="1" s="25">
       <c r="A276" s="9" t="n">
         <v>270</v>
       </c>
@@ -22325,11 +21510,8 @@
       <c r="W276" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X276" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="277" ht="13.55" customHeight="1" s="25">
       <c r="A277" s="9" t="n">
         <v>271</v>
       </c>
@@ -22401,11 +21583,8 @@
       <c r="W277" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X277" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="278" ht="13.55" customHeight="1" s="25">
       <c r="A278" s="9" t="n">
         <v>272</v>
       </c>
@@ -22477,11 +21656,8 @@
       <c r="W278" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X278" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="279" ht="13.55" customHeight="1" s="25">
       <c r="A279" s="9" t="n">
         <v>273</v>
       </c>
@@ -22553,11 +21729,8 @@
       <c r="W279" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X279" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="280" ht="13.55" customHeight="1" s="25">
       <c r="A280" s="9" t="n">
         <v>274</v>
       </c>
@@ -22629,11 +21802,8 @@
       <c r="W280" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X280" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="281" ht="13.55" customHeight="1" s="25">
       <c r="A281" s="9" t="n">
         <v>275</v>
       </c>
@@ -22705,11 +21875,8 @@
       <c r="W281" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X281" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="282" ht="13.55" customHeight="1" s="25">
       <c r="A282" s="9" t="n">
         <v>276</v>
       </c>
@@ -22781,11 +21948,8 @@
       <c r="W282" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X282" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="283" ht="13.55" customHeight="1" s="25">
       <c r="A283" s="9" t="n">
         <v>277</v>
       </c>
@@ -22857,11 +22021,8 @@
       <c r="W283" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X283" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="284" ht="13.55" customHeight="1" s="25">
       <c r="A284" s="9" t="n">
         <v>278</v>
       </c>
@@ -22933,11 +22094,8 @@
       <c r="W284" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X284" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="285" ht="13.55" customHeight="1" s="25">
       <c r="A285" s="9" t="n">
         <v>279</v>
       </c>
@@ -23009,11 +22167,8 @@
       <c r="W285" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X285" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="286" ht="13.55" customHeight="1" s="25">
       <c r="A286" s="9" t="n">
         <v>280</v>
       </c>
@@ -23085,11 +22240,8 @@
       <c r="W286" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X286" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="287" ht="13.55" customHeight="1" s="25">
       <c r="A287" s="9" t="n">
         <v>281</v>
       </c>
@@ -23161,11 +22313,8 @@
       <c r="W287" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X287" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="288" ht="13.55" customHeight="1" s="25">
       <c r="A288" s="9" t="n">
         <v>282</v>
       </c>
@@ -23237,11 +22386,8 @@
       <c r="W288" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X288" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="289" ht="13.55" customHeight="1" s="25">
       <c r="A289" s="9" t="n">
         <v>283</v>
       </c>
@@ -23313,11 +22459,8 @@
       <c r="W289" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X289" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="290" ht="13.55" customHeight="1" s="25">
       <c r="A290" s="9" t="n">
         <v>284</v>
       </c>
@@ -23389,11 +22532,8 @@
       <c r="W290" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X290" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="291" ht="13.55" customHeight="1" s="25">
       <c r="A291" s="9" t="n">
         <v>285</v>
       </c>
@@ -23465,11 +22605,8 @@
       <c r="W291" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X291" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="292" ht="13.55" customHeight="1" s="25">
       <c r="A292" s="9" t="n">
         <v>286</v>
       </c>
@@ -23541,11 +22678,8 @@
       <c r="W292" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X292" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="293" ht="13.55" customHeight="1" s="25">
       <c r="A293" s="9" t="n">
         <v>287</v>
       </c>
@@ -23617,11 +22751,8 @@
       <c r="W293" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X293" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="294" ht="13.55" customHeight="1" s="25">
       <c r="A294" s="9" t="n">
         <v>288</v>
       </c>
@@ -23693,11 +22824,8 @@
       <c r="W294" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X294" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="295" ht="13.55" customHeight="1" s="25">
       <c r="A295" s="9" t="n">
         <v>289</v>
       </c>
@@ -23769,11 +22897,8 @@
       <c r="W295" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X295" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="296" ht="13.55" customHeight="1" s="25">
       <c r="A296" s="9" t="n">
         <v>290</v>
       </c>
@@ -23845,11 +22970,8 @@
       <c r="W296" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X296" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="297" ht="13.55" customHeight="1" s="25">
       <c r="A297" s="9" t="n">
         <v>291</v>
       </c>
@@ -23921,11 +23043,8 @@
       <c r="W297" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X297" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="298" ht="13.55" customHeight="1" s="25">
       <c r="A298" s="9" t="n">
         <v>292</v>
       </c>
@@ -23997,11 +23116,8 @@
       <c r="W298" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X298" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="299" ht="13.55" customHeight="1" s="25">
       <c r="A299" s="9" t="n">
         <v>293</v>
       </c>
@@ -24073,11 +23189,8 @@
       <c r="W299" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X299" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="300" ht="13.55" customHeight="1" s="25">
       <c r="A300" s="9" t="n">
         <v>294</v>
       </c>
@@ -24149,11 +23262,8 @@
       <c r="W300" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X300" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="301" ht="13.55" customHeight="1" s="25">
       <c r="A301" s="9" t="n">
         <v>295</v>
       </c>
@@ -24225,11 +23335,8 @@
       <c r="W301" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X301" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="302" ht="13.55" customHeight="1" s="25">
       <c r="A302" s="9" t="n">
         <v>296</v>
       </c>
@@ -24301,11 +23408,8 @@
       <c r="W302" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X302" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="303" ht="13.55" customHeight="1" s="25">
       <c r="A303" s="9" t="n">
         <v>297</v>
       </c>
@@ -24377,11 +23481,8 @@
       <c r="W303" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X303" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="304" ht="13.55" customHeight="1" s="25">
       <c r="A304" s="9" t="n">
         <v>298</v>
       </c>
@@ -24453,11 +23554,8 @@
       <c r="W304" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X304" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="305" ht="13.55" customHeight="1" s="25">
       <c r="A305" s="9" t="n">
         <v>299</v>
       </c>
@@ -24529,11 +23627,8 @@
       <c r="W305" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X305" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="306" ht="13.55" customHeight="1" s="25">
       <c r="A306" s="9" t="n">
         <v>300</v>
       </c>
@@ -24605,11 +23700,8 @@
       <c r="W306" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X306" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="307" ht="13.55" customHeight="1" s="25">
       <c r="A307" s="9" t="n">
         <v>301</v>
       </c>
@@ -24681,11 +23773,8 @@
       <c r="W307" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X307" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="308" ht="13.55" customHeight="1" s="25">
       <c r="A308" s="9" t="n">
         <v>302</v>
       </c>
@@ -24757,11 +23846,8 @@
       <c r="W308" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X308" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="309" ht="13.55" customHeight="1" s="25">
       <c r="A309" s="9" t="n">
         <v>303</v>
       </c>
@@ -24833,11 +23919,8 @@
       <c r="W309" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X309" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="310" ht="13.55" customHeight="1" s="25">
       <c r="A310" s="9" t="n">
         <v>304</v>
       </c>
@@ -24909,11 +23992,8 @@
       <c r="W310" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X310" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="311" ht="13.55" customHeight="1" s="25">
       <c r="A311" s="9" t="n">
         <v>305</v>
       </c>
@@ -24985,11 +24065,8 @@
       <c r="W311" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X311" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="312" ht="13.55" customHeight="1" s="25">
       <c r="A312" s="9" t="n">
         <v>306</v>
       </c>
@@ -25061,11 +24138,8 @@
       <c r="W312" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X312" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="313" ht="13.55" customHeight="1" s="25">
       <c r="A313" s="9" t="n">
         <v>307</v>
       </c>
@@ -25137,11 +24211,8 @@
       <c r="W313" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X313" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="314" ht="13.55" customHeight="1" s="25">
       <c r="A314" s="9" t="n">
         <v>308</v>
       </c>
@@ -25213,11 +24284,8 @@
       <c r="W314" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X314" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="315" ht="13.55" customHeight="1" s="25">
       <c r="A315" s="9" t="n">
         <v>309</v>
       </c>
@@ -25289,11 +24357,8 @@
       <c r="W315" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X315" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="316" ht="13.55" customHeight="1" s="25">
       <c r="A316" s="9" t="n">
         <v>310</v>
       </c>
@@ -25365,11 +24430,8 @@
       <c r="W316" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X316" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="317" ht="13.55" customHeight="1" s="25">
       <c r="A317" s="9" t="n">
         <v>311</v>
       </c>
@@ -25441,11 +24503,8 @@
       <c r="W317" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X317" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" ht="13.55" customHeight="1" s="24">
+    </row>
+    <row r="318" ht="13.55" customHeight="1" s="25">
       <c r="A318" s="9" t="n">
         <v>312</v>
       </c>
@@ -25517,15 +24576,12 @@
       <c r="W318" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X318" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" ht="14.05" customHeight="1" s="24">
-      <c r="A319" s="12" t="n">
+    </row>
+    <row r="319" ht="14.05" customHeight="1" s="25">
+      <c r="A319" s="13" t="n">
         <v>313</v>
       </c>
-      <c r="B319" s="13" t="inlineStr">
+      <c r="B319" s="14" t="inlineStr">
         <is>
           <t>Karimnagar</t>
         </is>
@@ -25593,229 +24649,217 @@
       <c r="W319" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X319" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" ht="14.15" customHeight="1" s="24">
-      <c r="A320" s="14" t="inlineStr">
+    </row>
+    <row r="320" ht="14.15" customHeight="1" s="25">
+      <c r="A320" s="15" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B320" s="15" t="n"/>
-      <c r="C320" s="16" t="n">
+      <c r="B320" s="16" t="n"/>
+      <c r="C320" s="17" t="n">
         <v>728</v>
       </c>
-      <c r="D320" s="16" t="n">
+      <c r="D320" s="17" t="n">
         <v>68351</v>
       </c>
-      <c r="E320" s="16" t="n">
+      <c r="E320" s="17" t="n">
         <v>38384</v>
       </c>
-      <c r="F320" s="16" t="n">
+      <c r="F320" s="17" t="n">
         <v>5190</v>
       </c>
-      <c r="G320" s="16" t="n">
+      <c r="G320" s="17" t="n">
         <v>581</v>
       </c>
-      <c r="H320" s="16" t="n">
+      <c r="H320" s="17" t="n">
         <v>320</v>
       </c>
-      <c r="I320" s="16" t="n">
+      <c r="I320" s="17" t="n">
         <v>17777</v>
       </c>
-      <c r="J320" s="16" t="n">
+      <c r="J320" s="17" t="n">
         <v>2674</v>
       </c>
-      <c r="K320" s="16" t="n">
+      <c r="K320" s="17" t="n">
         <v>535</v>
       </c>
-      <c r="L320" s="16" t="n">
+      <c r="L320" s="17" t="n">
         <v>184</v>
       </c>
-      <c r="M320" s="16" t="n">
+      <c r="M320" s="17" t="n">
         <v>2139</v>
       </c>
-      <c r="N320" s="16" t="n">
+      <c r="N320" s="17" t="n">
         <v>461</v>
       </c>
-      <c r="O320" s="16" t="n">
+      <c r="O320" s="17" t="n">
         <v>562</v>
       </c>
-      <c r="P320" s="16" t="n">
+      <c r="P320" s="17" t="n">
         <v>208</v>
       </c>
-      <c r="Q320" s="16" t="n">
+      <c r="Q320" s="17" t="n">
         <v>363</v>
       </c>
-      <c r="R320" s="16" t="n">
+      <c r="R320" s="17" t="n">
         <v>455</v>
       </c>
-      <c r="S320" s="16" t="n">
+      <c r="S320" s="17" t="n">
         <v>510</v>
       </c>
-      <c r="T320" s="16" t="n">
+      <c r="T320" s="17" t="n">
         <v>139422</v>
       </c>
-      <c r="U320" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V320" s="16" t="n">
+      <c r="U320" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V320" s="17" t="n">
         <v>139422</v>
       </c>
-      <c r="W320" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X320" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" ht="13.65" customHeight="1" s="24">
-      <c r="A321" s="17" t="inlineStr">
+      <c r="W320" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" ht="13.65" customHeight="1" s="25">
+      <c r="A321" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
-      <c r="B321" s="18" t="n"/>
-      <c r="C321" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D321" s="16" t="n">
+      <c r="B321" s="19" t="n"/>
+      <c r="C321" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D321" s="17" t="n">
         <v>387</v>
       </c>
-      <c r="E321" s="16" t="n">
+      <c r="E321" s="17" t="n">
         <v>220</v>
       </c>
-      <c r="F321" s="16" t="n">
+      <c r="F321" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="G321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I321" s="16" t="n">
+      <c r="G321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="J321" s="16" t="n">
+      <c r="J321" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="K321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M321" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O321" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T321" s="16" t="n">
+      <c r="K321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" s="17" t="n">
         <v>701</v>
       </c>
-      <c r="U321" s="16" t="n">
+      <c r="U321" s="17" t="n">
         <v>242</v>
       </c>
-      <c r="V321" s="16" t="n">
+      <c r="V321" s="17" t="n">
         <v>943</v>
       </c>
-      <c r="W321" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X321" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" ht="13.65" customHeight="1" s="24">
-      <c r="A322" s="19" t="inlineStr">
+      <c r="W321" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" ht="13.65" customHeight="1" s="25">
+      <c r="A322" s="20" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B322" s="20" t="n"/>
-      <c r="C322" s="21" t="n">
+      <c r="B322" s="21" t="n"/>
+      <c r="C322" s="22" t="n">
         <v>729</v>
       </c>
-      <c r="D322" s="22" t="n">
+      <c r="D322" s="23" t="n">
         <v>68738</v>
       </c>
-      <c r="E322" s="22" t="n">
+      <c r="E322" s="23" t="n">
         <v>38604</v>
       </c>
-      <c r="F322" s="22" t="n">
+      <c r="F322" s="23" t="n">
         <v>5222</v>
       </c>
-      <c r="G322" s="22" t="n">
+      <c r="G322" s="23" t="n">
         <v>581</v>
       </c>
-      <c r="H322" s="22" t="n">
+      <c r="H322" s="23" t="n">
         <v>320</v>
       </c>
-      <c r="I322" s="22" t="n">
+      <c r="I322" s="23" t="n">
         <v>17794</v>
       </c>
-      <c r="J322" s="22" t="n">
+      <c r="J322" s="23" t="n">
         <v>2714</v>
       </c>
-      <c r="K322" s="22" t="n">
+      <c r="K322" s="23" t="n">
         <v>535</v>
       </c>
-      <c r="L322" s="22" t="n">
+      <c r="L322" s="23" t="n">
         <v>184</v>
       </c>
-      <c r="M322" s="22" t="n">
+      <c r="M322" s="23" t="n">
         <v>2141</v>
       </c>
-      <c r="N322" s="22" t="n">
+      <c r="N322" s="23" t="n">
         <v>461</v>
       </c>
-      <c r="O322" s="22" t="n">
+      <c r="O322" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="P322" s="22" t="n">
+      <c r="P322" s="23" t="n">
         <v>208</v>
       </c>
-      <c r="Q322" s="22" t="n">
+      <c r="Q322" s="23" t="n">
         <v>363</v>
       </c>
-      <c r="R322" s="22" t="n">
+      <c r="R322" s="23" t="n">
         <v>455</v>
       </c>
-      <c r="S322" s="22" t="n">
+      <c r="S322" s="23" t="n">
         <v>510</v>
       </c>
-      <c r="T322" s="22" t="n">
+      <c r="T322" s="23" t="n">
         <v>140123</v>
       </c>
-      <c r="U322" s="22" t="n">
+      <c r="U322" s="23" t="n">
         <v>242</v>
       </c>
-      <c r="V322" s="22" t="n">
+      <c r="V322" s="23" t="n">
         <v>140365</v>
       </c>
-      <c r="W322" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X322" s="23" t="n">
+      <c r="W322" s="24" t="n">
         <v>0</v>
       </c>
     </row>
